--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,3104 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123126012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>433691</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7068902</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123126015</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>433714</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7068855</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123126031</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>433679</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7068621</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123126029</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>433762</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7068668</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123126041</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90970</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>433610</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7068788</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123126036</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>433681</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7068744</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123126013</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>433669</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7068887</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123126007</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>433613</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7068884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123126034</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>433666</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7068732</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123126021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>433738</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7068735</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123126024</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>433794</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7068730</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123126009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>433602</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7068916</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123126035</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>433677</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7068737</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123126039</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>433621</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7068773</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123126030</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>433770</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7068647</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123126017</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>433722</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7068798</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123126040</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>433621</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7068780</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123126018</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>433754</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7068779</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123126014</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>433715</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7068850</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123126019</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>433752</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7068781</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123126011</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>433698</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7068902</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123126008</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>433615</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7068906</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123126038</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>433606</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7068765</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123126032</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>433626</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7068579</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123126020</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>433773</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7068763</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123126028</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>433775</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7068594</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123126023</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>433765</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7068743</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123126026</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>433798</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7068699</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123126010</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>433601</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7068918</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126012</v>
+        <v>123126032</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433691</v>
+        <v>433626</v>
       </c>
       <c r="R4" t="n">
-        <v>7068902</v>
+        <v>7068579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126015</v>
+        <v>123126013</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433714</v>
+        <v>433669</v>
       </c>
       <c r="R5" t="n">
-        <v>7068855</v>
+        <v>7068887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126031</v>
+        <v>123126035</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433679</v>
+        <v>433677</v>
       </c>
       <c r="R6" t="n">
-        <v>7068621</v>
+        <v>7068737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126029</v>
+        <v>123126010</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433762</v>
+        <v>433601</v>
       </c>
       <c r="R7" t="n">
-        <v>7068668</v>
+        <v>7068918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126041</v>
+        <v>123126030</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433610</v>
+        <v>433770</v>
       </c>
       <c r="R8" t="n">
-        <v>7068788</v>
+        <v>7068647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126036</v>
+        <v>123126029</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1477,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433681</v>
+        <v>433762</v>
       </c>
       <c r="R9" t="n">
-        <v>7068744</v>
+        <v>7068668</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126013</v>
+        <v>123126023</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1584,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433669</v>
+        <v>433765</v>
       </c>
       <c r="R10" t="n">
-        <v>7068887</v>
+        <v>7068743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126034</v>
+        <v>123126041</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433666</v>
+        <v>433610</v>
       </c>
       <c r="R12" t="n">
-        <v>7068732</v>
+        <v>7068788</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,11 +1839,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,7 +1865,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126021</v>
+        <v>123126024</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433738</v>
+        <v>433794</v>
       </c>
       <c r="R13" t="n">
-        <v>7068735</v>
+        <v>7068730</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1972,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126024</v>
+        <v>123126011</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433794</v>
+        <v>433698</v>
       </c>
       <c r="R14" t="n">
-        <v>7068730</v>
+        <v>7068902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126009</v>
+        <v>123126026</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433602</v>
+        <v>433798</v>
       </c>
       <c r="R15" t="n">
-        <v>7068916</v>
+        <v>7068699</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126035</v>
+        <v>123126031</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433677</v>
+        <v>433679</v>
       </c>
       <c r="R16" t="n">
-        <v>7068737</v>
+        <v>7068621</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126039</v>
+        <v>123126038</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433621</v>
+        <v>433606</v>
       </c>
       <c r="R17" t="n">
-        <v>7068773</v>
+        <v>7068765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126030</v>
+        <v>123126014</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433770</v>
+        <v>433715</v>
       </c>
       <c r="R18" t="n">
-        <v>7068647</v>
+        <v>7068850</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126017</v>
+        <v>123126036</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433722</v>
+        <v>433681</v>
       </c>
       <c r="R19" t="n">
-        <v>7068798</v>
+        <v>7068744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126040</v>
+        <v>123126015</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433621</v>
+        <v>433714</v>
       </c>
       <c r="R20" t="n">
-        <v>7068780</v>
+        <v>7068855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126018</v>
+        <v>123126020</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433754</v>
+        <v>433773</v>
       </c>
       <c r="R21" t="n">
-        <v>7068779</v>
+        <v>7068763</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126014</v>
+        <v>123126009</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433715</v>
+        <v>433602</v>
       </c>
       <c r="R22" t="n">
-        <v>7068850</v>
+        <v>7068916</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126019</v>
+        <v>123126018</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433752</v>
+        <v>433754</v>
       </c>
       <c r="R23" t="n">
-        <v>7068781</v>
+        <v>7068779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126011</v>
+        <v>123126021</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433698</v>
+        <v>433738</v>
       </c>
       <c r="R24" t="n">
-        <v>7068902</v>
+        <v>7068735</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126008</v>
+        <v>123126019</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433615</v>
+        <v>433752</v>
       </c>
       <c r="R25" t="n">
-        <v>7068906</v>
+        <v>7068781</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,7 +3256,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126038</v>
+        <v>123126040</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433606</v>
+        <v>433621</v>
       </c>
       <c r="R26" t="n">
-        <v>7068765</v>
+        <v>7068780</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126032</v>
+        <v>123126028</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433626</v>
+        <v>433775</v>
       </c>
       <c r="R27" t="n">
-        <v>7068579</v>
+        <v>7068594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126020</v>
+        <v>123126008</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433773</v>
+        <v>433615</v>
       </c>
       <c r="R28" t="n">
-        <v>7068763</v>
+        <v>7068906</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126028</v>
+        <v>123126039</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433775</v>
+        <v>433621</v>
       </c>
       <c r="R29" t="n">
-        <v>7068594</v>
+        <v>7068773</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126023</v>
+        <v>123126012</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433765</v>
+        <v>433691</v>
       </c>
       <c r="R30" t="n">
-        <v>7068743</v>
+        <v>7068902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126026</v>
+        <v>123126017</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433798</v>
+        <v>433722</v>
       </c>
       <c r="R31" t="n">
-        <v>7068699</v>
+        <v>7068798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126010</v>
+        <v>123126034</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433601</v>
+        <v>433666</v>
       </c>
       <c r="R32" t="n">
-        <v>7068918</v>
+        <v>7068732</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126032</v>
+        <v>123126040</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433626</v>
+        <v>433621</v>
       </c>
       <c r="R4" t="n">
-        <v>7068579</v>
+        <v>7068780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126013</v>
+        <v>123126009</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433669</v>
+        <v>433602</v>
       </c>
       <c r="R5" t="n">
-        <v>7068887</v>
+        <v>7068916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126035</v>
+        <v>123126028</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433677</v>
+        <v>433775</v>
       </c>
       <c r="R6" t="n">
-        <v>7068737</v>
+        <v>7068594</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126010</v>
+        <v>123126031</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433601</v>
+        <v>433679</v>
       </c>
       <c r="R7" t="n">
-        <v>7068918</v>
+        <v>7068621</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126030</v>
+        <v>123126008</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433770</v>
+        <v>433615</v>
       </c>
       <c r="R8" t="n">
-        <v>7068647</v>
+        <v>7068906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126029</v>
+        <v>123126017</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433762</v>
+        <v>433722</v>
       </c>
       <c r="R9" t="n">
-        <v>7068668</v>
+        <v>7068798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126023</v>
+        <v>123126021</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433765</v>
+        <v>433738</v>
       </c>
       <c r="R10" t="n">
-        <v>7068743</v>
+        <v>7068735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126007</v>
+        <v>123126039</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433613</v>
+        <v>433621</v>
       </c>
       <c r="R11" t="n">
-        <v>7068884</v>
+        <v>7068773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126041</v>
+        <v>123126030</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433610</v>
+        <v>433770</v>
       </c>
       <c r="R12" t="n">
-        <v>7068788</v>
+        <v>7068647</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,6 +1839,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126024</v>
+        <v>123126012</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1905,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433794</v>
+        <v>433691</v>
       </c>
       <c r="R13" t="n">
-        <v>7068730</v>
+        <v>7068902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126011</v>
+        <v>123126018</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -2012,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433698</v>
+        <v>433754</v>
       </c>
       <c r="R14" t="n">
-        <v>7068902</v>
+        <v>7068779</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126026</v>
+        <v>123126038</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2119,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433798</v>
+        <v>433606</v>
       </c>
       <c r="R15" t="n">
-        <v>7068699</v>
+        <v>7068765</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2191,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126031</v>
+        <v>123126029</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433679</v>
+        <v>433762</v>
       </c>
       <c r="R16" t="n">
-        <v>7068621</v>
+        <v>7068668</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126038</v>
+        <v>123126035</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2333,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433606</v>
+        <v>433677</v>
       </c>
       <c r="R17" t="n">
-        <v>7068765</v>
+        <v>7068737</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126014</v>
+        <v>123126032</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2440,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433715</v>
+        <v>433626</v>
       </c>
       <c r="R18" t="n">
-        <v>7068850</v>
+        <v>7068579</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2512,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126036</v>
+        <v>123126020</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2547,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433681</v>
+        <v>433773</v>
       </c>
       <c r="R19" t="n">
-        <v>7068744</v>
+        <v>7068763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,7 +2619,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126015</v>
+        <v>123126024</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2654,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433714</v>
+        <v>433794</v>
       </c>
       <c r="R20" t="n">
-        <v>7068855</v>
+        <v>7068730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,7 +2699,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,7 +2726,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126020</v>
+        <v>123126036</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433773</v>
+        <v>433681</v>
       </c>
       <c r="R21" t="n">
-        <v>7068763</v>
+        <v>7068744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,7 +2806,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,7 +2833,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126009</v>
+        <v>123126011</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2868,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433602</v>
+        <v>433698</v>
       </c>
       <c r="R22" t="n">
-        <v>7068916</v>
+        <v>7068902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126018</v>
+        <v>123126014</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433754</v>
+        <v>433715</v>
       </c>
       <c r="R23" t="n">
-        <v>7068779</v>
+        <v>7068850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,7 +3047,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126021</v>
+        <v>123126010</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3082,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433738</v>
+        <v>433601</v>
       </c>
       <c r="R24" t="n">
-        <v>7068735</v>
+        <v>7068918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,7 +3261,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126040</v>
+        <v>123126026</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433621</v>
+        <v>433798</v>
       </c>
       <c r="R26" t="n">
-        <v>7068780</v>
+        <v>7068699</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3341,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,7 +3368,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126028</v>
+        <v>123126023</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3403,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433775</v>
+        <v>433765</v>
       </c>
       <c r="R27" t="n">
-        <v>7068594</v>
+        <v>7068743</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3475,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126008</v>
+        <v>123126007</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3510,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433615</v>
+        <v>433613</v>
       </c>
       <c r="R28" t="n">
-        <v>7068906</v>
+        <v>7068884</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,7 +3582,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126039</v>
+        <v>123126034</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433621</v>
+        <v>433666</v>
       </c>
       <c r="R29" t="n">
-        <v>7068773</v>
+        <v>7068732</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3662,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,10 +3689,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126012</v>
+        <v>123126041</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3700,21 +3705,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3724,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433691</v>
+        <v>433610</v>
       </c>
       <c r="R30" t="n">
-        <v>7068902</v>
+        <v>7068788</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3760,11 +3765,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126017</v>
+        <v>123126015</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433722</v>
+        <v>433714</v>
       </c>
       <c r="R31" t="n">
-        <v>7068798</v>
+        <v>7068855</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126034</v>
+        <v>123126013</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433666</v>
+        <v>433669</v>
       </c>
       <c r="R32" t="n">
-        <v>7068732</v>
+        <v>7068887</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -2726,7 +2726,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126036</v>
+        <v>123126014</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433681</v>
+        <v>433715</v>
       </c>
       <c r="R21" t="n">
-        <v>7068744</v>
+        <v>7068850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126011</v>
+        <v>123126010</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433698</v>
+        <v>433601</v>
       </c>
       <c r="R22" t="n">
-        <v>7068902</v>
+        <v>7068918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126014</v>
+        <v>123126036</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433715</v>
+        <v>433681</v>
       </c>
       <c r="R23" t="n">
-        <v>7068850</v>
+        <v>7068744</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126010</v>
+        <v>123126011</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433601</v>
+        <v>433698</v>
       </c>
       <c r="R24" t="n">
-        <v>7068918</v>
+        <v>7068902</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3689,10 +3689,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126041</v>
+        <v>123126015</v>
       </c>
       <c r="B30" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433610</v>
+        <v>433714</v>
       </c>
       <c r="R30" t="n">
-        <v>7068788</v>
+        <v>7068855</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3765,6 +3765,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,10 +3796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126015</v>
+        <v>123126041</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3807,21 +3812,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3831,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433714</v>
+        <v>433610</v>
       </c>
       <c r="R31" t="n">
-        <v>7068855</v>
+        <v>7068788</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3867,11 +3872,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -2726,7 +2726,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126014</v>
+        <v>123126036</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433715</v>
+        <v>433681</v>
       </c>
       <c r="R21" t="n">
-        <v>7068850</v>
+        <v>7068744</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126010</v>
+        <v>123126011</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433601</v>
+        <v>433698</v>
       </c>
       <c r="R22" t="n">
-        <v>7068918</v>
+        <v>7068902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126036</v>
+        <v>123126014</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433681</v>
+        <v>433715</v>
       </c>
       <c r="R23" t="n">
-        <v>7068744</v>
+        <v>7068850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126011</v>
+        <v>123126010</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433698</v>
+        <v>433601</v>
       </c>
       <c r="R24" t="n">
-        <v>7068902</v>
+        <v>7068918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126040</v>
+        <v>123126017</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433621</v>
+        <v>433722</v>
       </c>
       <c r="R4" t="n">
-        <v>7068780</v>
+        <v>7068798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126009</v>
+        <v>123126023</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433602</v>
+        <v>433765</v>
       </c>
       <c r="R5" t="n">
-        <v>7068916</v>
+        <v>7068743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126028</v>
+        <v>123126024</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433775</v>
+        <v>433794</v>
       </c>
       <c r="R6" t="n">
-        <v>7068594</v>
+        <v>7068730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126031</v>
+        <v>123126040</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433679</v>
+        <v>433621</v>
       </c>
       <c r="R7" t="n">
-        <v>7068621</v>
+        <v>7068780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126008</v>
+        <v>123126021</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433615</v>
+        <v>433738</v>
       </c>
       <c r="R8" t="n">
-        <v>7068906</v>
+        <v>7068735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126017</v>
+        <v>123126014</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433722</v>
+        <v>433715</v>
       </c>
       <c r="R9" t="n">
-        <v>7068798</v>
+        <v>7068850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126021</v>
+        <v>123126031</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433738</v>
+        <v>433679</v>
       </c>
       <c r="R10" t="n">
-        <v>7068735</v>
+        <v>7068621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126039</v>
+        <v>123126038</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433621</v>
+        <v>433606</v>
       </c>
       <c r="R11" t="n">
-        <v>7068773</v>
+        <v>7068765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126030</v>
+        <v>123126028</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433770</v>
+        <v>433775</v>
       </c>
       <c r="R12" t="n">
-        <v>7068647</v>
+        <v>7068594</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126012</v>
+        <v>123126034</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433691</v>
+        <v>433666</v>
       </c>
       <c r="R13" t="n">
-        <v>7068902</v>
+        <v>7068732</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126018</v>
+        <v>123126041</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433754</v>
+        <v>433610</v>
       </c>
       <c r="R14" t="n">
-        <v>7068779</v>
+        <v>7068788</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,11 +2053,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2079,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126038</v>
+        <v>123126015</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2124,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433606</v>
+        <v>433714</v>
       </c>
       <c r="R15" t="n">
-        <v>7068765</v>
+        <v>7068855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2159,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2186,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126029</v>
+        <v>123126039</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2231,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433762</v>
+        <v>433621</v>
       </c>
       <c r="R16" t="n">
-        <v>7068668</v>
+        <v>7068773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2266,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126035</v>
+        <v>123126009</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433677</v>
+        <v>433602</v>
       </c>
       <c r="R17" t="n">
-        <v>7068737</v>
+        <v>7068916</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126032</v>
+        <v>123126019</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2445,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433626</v>
+        <v>433752</v>
       </c>
       <c r="R18" t="n">
-        <v>7068579</v>
+        <v>7068781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126020</v>
+        <v>123126036</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2552,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433773</v>
+        <v>433681</v>
       </c>
       <c r="R19" t="n">
-        <v>7068763</v>
+        <v>7068744</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2587,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2614,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126024</v>
+        <v>123126035</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2659,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433794</v>
+        <v>433677</v>
       </c>
       <c r="R20" t="n">
-        <v>7068730</v>
+        <v>7068737</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2694,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126036</v>
+        <v>123126026</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433681</v>
+        <v>433798</v>
       </c>
       <c r="R21" t="n">
-        <v>7068744</v>
+        <v>7068699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126014</v>
+        <v>123126010</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433715</v>
+        <v>433601</v>
       </c>
       <c r="R23" t="n">
-        <v>7068850</v>
+        <v>7068918</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126010</v>
+        <v>123126012</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3087,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433601</v>
+        <v>433691</v>
       </c>
       <c r="R24" t="n">
-        <v>7068918</v>
+        <v>7068902</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126019</v>
+        <v>123126032</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433752</v>
+        <v>433626</v>
       </c>
       <c r="R25" t="n">
-        <v>7068781</v>
+        <v>7068579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3256,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126026</v>
+        <v>123126008</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433798</v>
+        <v>433615</v>
       </c>
       <c r="R26" t="n">
-        <v>7068699</v>
+        <v>7068906</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,7 +3336,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,7 +3363,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126023</v>
+        <v>123126013</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433765</v>
+        <v>433669</v>
       </c>
       <c r="R27" t="n">
-        <v>7068743</v>
+        <v>7068887</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3448,7 +3443,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3475,7 +3470,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126007</v>
+        <v>123126029</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3515,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433613</v>
+        <v>433762</v>
       </c>
       <c r="R28" t="n">
-        <v>7068884</v>
+        <v>7068668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3582,7 +3577,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126034</v>
+        <v>123126007</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433666</v>
+        <v>433613</v>
       </c>
       <c r="R29" t="n">
-        <v>7068732</v>
+        <v>7068884</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3689,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126015</v>
+        <v>123126018</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433714</v>
+        <v>433754</v>
       </c>
       <c r="R30" t="n">
-        <v>7068855</v>
+        <v>7068779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3796,10 +3791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126041</v>
+        <v>123126030</v>
       </c>
       <c r="B31" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,21 +3807,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433610</v>
+        <v>433770</v>
       </c>
       <c r="R31" t="n">
-        <v>7068788</v>
+        <v>7068647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3872,6 +3867,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126013</v>
+        <v>123126020</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433669</v>
+        <v>433773</v>
       </c>
       <c r="R32" t="n">
-        <v>7068887</v>
+        <v>7068763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126017</v>
+        <v>123126010</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433722</v>
+        <v>433601</v>
       </c>
       <c r="R4" t="n">
-        <v>7068798</v>
+        <v>7068918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126023</v>
+        <v>123126031</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433765</v>
+        <v>433679</v>
       </c>
       <c r="R5" t="n">
-        <v>7068743</v>
+        <v>7068621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126024</v>
+        <v>123126036</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433794</v>
+        <v>433681</v>
       </c>
       <c r="R6" t="n">
-        <v>7068730</v>
+        <v>7068744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126040</v>
+        <v>123126041</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433621</v>
+        <v>433610</v>
       </c>
       <c r="R7" t="n">
-        <v>7068780</v>
+        <v>7068788</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1304,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1330,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126021</v>
+        <v>123126039</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433738</v>
+        <v>433621</v>
       </c>
       <c r="R8" t="n">
-        <v>7068735</v>
+        <v>7068773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1410,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126014</v>
+        <v>123126035</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433715</v>
+        <v>433677</v>
       </c>
       <c r="R9" t="n">
-        <v>7068850</v>
+        <v>7068737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1517,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1544,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126031</v>
+        <v>123126030</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1589,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433679</v>
+        <v>433770</v>
       </c>
       <c r="R10" t="n">
-        <v>7068621</v>
+        <v>7068647</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1651,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126038</v>
+        <v>123126012</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1696,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433606</v>
+        <v>433691</v>
       </c>
       <c r="R11" t="n">
-        <v>7068765</v>
+        <v>7068902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1731,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126028</v>
+        <v>123126032</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1803,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433775</v>
+        <v>433626</v>
       </c>
       <c r="R12" t="n">
-        <v>7068594</v>
+        <v>7068579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1865,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126034</v>
+        <v>123126026</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433666</v>
+        <v>433798</v>
       </c>
       <c r="R13" t="n">
-        <v>7068732</v>
+        <v>7068699</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126041</v>
+        <v>123126023</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433610</v>
+        <v>433765</v>
       </c>
       <c r="R14" t="n">
-        <v>7068788</v>
+        <v>7068743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,6 +2048,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,7 +2079,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126015</v>
+        <v>123126034</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433714</v>
+        <v>433666</v>
       </c>
       <c r="R15" t="n">
-        <v>7068855</v>
+        <v>7068732</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126039</v>
+        <v>123126013</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433621</v>
+        <v>433669</v>
       </c>
       <c r="R16" t="n">
-        <v>7068773</v>
+        <v>7068887</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126009</v>
+        <v>123126020</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433602</v>
+        <v>433773</v>
       </c>
       <c r="R17" t="n">
-        <v>7068916</v>
+        <v>7068763</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126019</v>
+        <v>123126029</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433752</v>
+        <v>433762</v>
       </c>
       <c r="R18" t="n">
-        <v>7068781</v>
+        <v>7068668</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126036</v>
+        <v>123126011</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433681</v>
+        <v>433698</v>
       </c>
       <c r="R19" t="n">
-        <v>7068744</v>
+        <v>7068902</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126035</v>
+        <v>123126028</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433677</v>
+        <v>433775</v>
       </c>
       <c r="R20" t="n">
-        <v>7068737</v>
+        <v>7068594</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126026</v>
+        <v>123126024</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433798</v>
+        <v>433794</v>
       </c>
       <c r="R21" t="n">
-        <v>7068699</v>
+        <v>7068730</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126011</v>
+        <v>123126015</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433698</v>
+        <v>433714</v>
       </c>
       <c r="R22" t="n">
-        <v>7068902</v>
+        <v>7068855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126010</v>
+        <v>123126040</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433601</v>
+        <v>433621</v>
       </c>
       <c r="R23" t="n">
-        <v>7068918</v>
+        <v>7068780</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126012</v>
+        <v>123126021</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433691</v>
+        <v>433738</v>
       </c>
       <c r="R24" t="n">
-        <v>7068902</v>
+        <v>7068735</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126032</v>
+        <v>123126007</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433626</v>
+        <v>433613</v>
       </c>
       <c r="R25" t="n">
-        <v>7068579</v>
+        <v>7068884</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126013</v>
+        <v>123126018</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433669</v>
+        <v>433754</v>
       </c>
       <c r="R27" t="n">
-        <v>7068887</v>
+        <v>7068779</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126029</v>
+        <v>123126038</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433762</v>
+        <v>433606</v>
       </c>
       <c r="R28" t="n">
-        <v>7068668</v>
+        <v>7068765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126007</v>
+        <v>123126017</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433613</v>
+        <v>433722</v>
       </c>
       <c r="R29" t="n">
-        <v>7068884</v>
+        <v>7068798</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126018</v>
+        <v>123126014</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433754</v>
+        <v>433715</v>
       </c>
       <c r="R30" t="n">
-        <v>7068779</v>
+        <v>7068850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126030</v>
+        <v>123126019</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433770</v>
+        <v>433752</v>
       </c>
       <c r="R31" t="n">
-        <v>7068647</v>
+        <v>7068781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126020</v>
+        <v>123126009</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433773</v>
+        <v>433602</v>
       </c>
       <c r="R32" t="n">
-        <v>7068763</v>
+        <v>7068916</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126010</v>
+        <v>123126008</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433601</v>
+        <v>433615</v>
       </c>
       <c r="R4" t="n">
-        <v>7068918</v>
+        <v>7068906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126031</v>
+        <v>123126014</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433679</v>
+        <v>433715</v>
       </c>
       <c r="R5" t="n">
-        <v>7068621</v>
+        <v>7068850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126036</v>
+        <v>123126009</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433681</v>
+        <v>433602</v>
       </c>
       <c r="R6" t="n">
-        <v>7068744</v>
+        <v>7068916</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126041</v>
+        <v>123126012</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433610</v>
+        <v>433691</v>
       </c>
       <c r="R7" t="n">
-        <v>7068788</v>
+        <v>7068902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126039</v>
+        <v>123126010</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433621</v>
+        <v>433601</v>
       </c>
       <c r="R8" t="n">
-        <v>7068773</v>
+        <v>7068918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126035</v>
+        <v>123126013</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433677</v>
+        <v>433669</v>
       </c>
       <c r="R9" t="n">
-        <v>7068737</v>
+        <v>7068887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126030</v>
+        <v>123126018</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433770</v>
+        <v>433754</v>
       </c>
       <c r="R10" t="n">
-        <v>7068647</v>
+        <v>7068779</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126012</v>
+        <v>123126019</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433691</v>
+        <v>433752</v>
       </c>
       <c r="R11" t="n">
-        <v>7068902</v>
+        <v>7068781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126032</v>
+        <v>123126007</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433626</v>
+        <v>433613</v>
       </c>
       <c r="R12" t="n">
-        <v>7068579</v>
+        <v>7068884</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126026</v>
+        <v>123126020</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433798</v>
+        <v>433773</v>
       </c>
       <c r="R13" t="n">
-        <v>7068699</v>
+        <v>7068763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126023</v>
+        <v>123126031</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433765</v>
+        <v>433679</v>
       </c>
       <c r="R14" t="n">
-        <v>7068743</v>
+        <v>7068621</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126034</v>
+        <v>123126029</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433666</v>
+        <v>433762</v>
       </c>
       <c r="R15" t="n">
-        <v>7068732</v>
+        <v>7068668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126013</v>
+        <v>123126035</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433669</v>
+        <v>433677</v>
       </c>
       <c r="R16" t="n">
-        <v>7068887</v>
+        <v>7068737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126020</v>
+        <v>123126017</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433773</v>
+        <v>433722</v>
       </c>
       <c r="R17" t="n">
-        <v>7068763</v>
+        <v>7068798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126029</v>
+        <v>123126028</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433762</v>
+        <v>433775</v>
       </c>
       <c r="R18" t="n">
-        <v>7068668</v>
+        <v>7068594</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2515,7 @@
         <v>123126011</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2614,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126028</v>
+        <v>123126021</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433775</v>
+        <v>433738</v>
       </c>
       <c r="R20" t="n">
-        <v>7068594</v>
+        <v>7068735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,10 +2726,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126024</v>
+        <v>123126026</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433794</v>
+        <v>433798</v>
       </c>
       <c r="R21" t="n">
-        <v>7068730</v>
+        <v>7068699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126015</v>
+        <v>123126039</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433714</v>
+        <v>433621</v>
       </c>
       <c r="R22" t="n">
-        <v>7068855</v>
+        <v>7068773</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,7 +2943,7 @@
         <v>123126040</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126021</v>
+        <v>123126034</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433738</v>
+        <v>433666</v>
       </c>
       <c r="R24" t="n">
-        <v>7068735</v>
+        <v>7068732</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126007</v>
+        <v>123126030</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433613</v>
+        <v>433770</v>
       </c>
       <c r="R25" t="n">
-        <v>7068884</v>
+        <v>7068647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,10 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126008</v>
+        <v>123126036</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433615</v>
+        <v>433681</v>
       </c>
       <c r="R26" t="n">
-        <v>7068906</v>
+        <v>7068744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3341,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,10 +3368,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126018</v>
+        <v>123126041</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>90973</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3379,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3403,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433754</v>
+        <v>433610</v>
       </c>
       <c r="R27" t="n">
-        <v>7068779</v>
+        <v>7068788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,11 +3444,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,10 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126038</v>
+        <v>123126032</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433606</v>
+        <v>433626</v>
       </c>
       <c r="R28" t="n">
-        <v>7068765</v>
+        <v>7068579</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126017</v>
+        <v>123126038</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433722</v>
+        <v>433606</v>
       </c>
       <c r="R29" t="n">
-        <v>7068798</v>
+        <v>7068765</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126014</v>
+        <v>123126023</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433715</v>
+        <v>433765</v>
       </c>
       <c r="R30" t="n">
-        <v>7068850</v>
+        <v>7068743</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,10 +3791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126019</v>
+        <v>123126024</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433752</v>
+        <v>433794</v>
       </c>
       <c r="R31" t="n">
-        <v>7068781</v>
+        <v>7068730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,10 +3898,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126009</v>
+        <v>123126015</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433602</v>
+        <v>433714</v>
       </c>
       <c r="R32" t="n">
-        <v>7068916</v>
+        <v>7068855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126008</v>
+        <v>123126019</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433615</v>
+        <v>433752</v>
       </c>
       <c r="R4" t="n">
-        <v>7068906</v>
+        <v>7068781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126014</v>
+        <v>123126010</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433715</v>
+        <v>433601</v>
       </c>
       <c r="R5" t="n">
-        <v>7068850</v>
+        <v>7068918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126009</v>
+        <v>123126034</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433602</v>
+        <v>433666</v>
       </c>
       <c r="R6" t="n">
-        <v>7068916</v>
+        <v>7068732</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126012</v>
+        <v>123126024</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433691</v>
+        <v>433794</v>
       </c>
       <c r="R7" t="n">
-        <v>7068902</v>
+        <v>7068730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126010</v>
+        <v>123126013</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433601</v>
+        <v>433669</v>
       </c>
       <c r="R8" t="n">
-        <v>7068918</v>
+        <v>7068887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126013</v>
+        <v>123126032</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433669</v>
+        <v>433626</v>
       </c>
       <c r="R9" t="n">
-        <v>7068887</v>
+        <v>7068579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126018</v>
+        <v>123126023</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433754</v>
+        <v>433765</v>
       </c>
       <c r="R10" t="n">
-        <v>7068779</v>
+        <v>7068743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126019</v>
+        <v>123126008</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433752</v>
+        <v>433615</v>
       </c>
       <c r="R11" t="n">
-        <v>7068781</v>
+        <v>7068906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126007</v>
+        <v>123126020</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433613</v>
+        <v>433773</v>
       </c>
       <c r="R12" t="n">
-        <v>7068884</v>
+        <v>7068763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126020</v>
+        <v>123126009</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433773</v>
+        <v>433602</v>
       </c>
       <c r="R13" t="n">
-        <v>7068763</v>
+        <v>7068916</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126031</v>
+        <v>123126012</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433679</v>
+        <v>433691</v>
       </c>
       <c r="R14" t="n">
-        <v>7068621</v>
+        <v>7068902</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126029</v>
+        <v>123126017</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433762</v>
+        <v>433722</v>
       </c>
       <c r="R15" t="n">
-        <v>7068668</v>
+        <v>7068798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126035</v>
+        <v>123126014</v>
       </c>
       <c r="B16" t="n">
         <v>57481</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433677</v>
+        <v>433715</v>
       </c>
       <c r="R16" t="n">
-        <v>7068737</v>
+        <v>7068850</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126017</v>
+        <v>123126039</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433722</v>
+        <v>433621</v>
       </c>
       <c r="R17" t="n">
-        <v>7068798</v>
+        <v>7068773</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126028</v>
+        <v>123126031</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433775</v>
+        <v>433679</v>
       </c>
       <c r="R18" t="n">
-        <v>7068594</v>
+        <v>7068621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2512,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126011</v>
+        <v>123126028</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433698</v>
+        <v>433775</v>
       </c>
       <c r="R19" t="n">
-        <v>7068902</v>
+        <v>7068594</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126021</v>
+        <v>123126026</v>
       </c>
       <c r="B20" t="n">
         <v>57481</v>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433738</v>
+        <v>433798</v>
       </c>
       <c r="R20" t="n">
-        <v>7068735</v>
+        <v>7068699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,7 +2726,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126026</v>
+        <v>123126029</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433798</v>
+        <v>433762</v>
       </c>
       <c r="R21" t="n">
-        <v>7068699</v>
+        <v>7068668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,7 +2833,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126039</v>
+        <v>123126030</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433621</v>
+        <v>433770</v>
       </c>
       <c r="R22" t="n">
-        <v>7068773</v>
+        <v>7068647</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2940,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126040</v>
+        <v>123126018</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433621</v>
+        <v>433754</v>
       </c>
       <c r="R23" t="n">
-        <v>7068780</v>
+        <v>7068779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,7 +3047,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126034</v>
+        <v>123126036</v>
       </c>
       <c r="B24" t="n">
         <v>57481</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433666</v>
+        <v>433681</v>
       </c>
       <c r="R24" t="n">
-        <v>7068732</v>
+        <v>7068744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,7 +3154,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126030</v>
+        <v>123126040</v>
       </c>
       <c r="B25" t="n">
         <v>57481</v>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433770</v>
+        <v>433621</v>
       </c>
       <c r="R25" t="n">
-        <v>7068647</v>
+        <v>7068780</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126036</v>
+        <v>123126007</v>
       </c>
       <c r="B26" t="n">
         <v>57481</v>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433681</v>
+        <v>433613</v>
       </c>
       <c r="R26" t="n">
-        <v>7068744</v>
+        <v>7068884</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3368,10 +3368,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126041</v>
+        <v>123126021</v>
       </c>
       <c r="B27" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433610</v>
+        <v>433738</v>
       </c>
       <c r="R27" t="n">
-        <v>7068788</v>
+        <v>7068735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,6 +3444,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,7 +3475,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126032</v>
+        <v>123126035</v>
       </c>
       <c r="B28" t="n">
         <v>57481</v>
@@ -3510,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433626</v>
+        <v>433677</v>
       </c>
       <c r="R28" t="n">
-        <v>7068579</v>
+        <v>7068737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,10 +3582,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126038</v>
+        <v>123126041</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3593,21 +3598,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3617,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433606</v>
+        <v>433610</v>
       </c>
       <c r="R29" t="n">
-        <v>7068765</v>
+        <v>7068788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,11 +3658,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126023</v>
+        <v>123126011</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433765</v>
+        <v>433698</v>
       </c>
       <c r="R30" t="n">
-        <v>7068743</v>
+        <v>7068902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126024</v>
+        <v>123126015</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433794</v>
+        <v>433714</v>
       </c>
       <c r="R31" t="n">
-        <v>7068730</v>
+        <v>7068855</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126015</v>
+        <v>123126038</v>
       </c>
       <c r="B32" t="n">
         <v>57481</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433714</v>
+        <v>433606</v>
       </c>
       <c r="R32" t="n">
-        <v>7068855</v>
+        <v>7068765</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -3684,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126011</v>
+        <v>123126015</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433698</v>
+        <v>433714</v>
       </c>
       <c r="R30" t="n">
-        <v>7068902</v>
+        <v>7068855</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126015</v>
+        <v>123126011</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433714</v>
+        <v>433698</v>
       </c>
       <c r="R31" t="n">
-        <v>7068855</v>
+        <v>7068902</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126019</v>
+        <v>123126039</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433752</v>
+        <v>433621</v>
       </c>
       <c r="R4" t="n">
-        <v>7068781</v>
+        <v>7068773</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126010</v>
+        <v>123126011</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433601</v>
+        <v>433698</v>
       </c>
       <c r="R5" t="n">
-        <v>7068918</v>
+        <v>7068902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126034</v>
+        <v>123126029</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433666</v>
+        <v>433762</v>
       </c>
       <c r="R6" t="n">
-        <v>7068732</v>
+        <v>7068668</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126024</v>
+        <v>123126026</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433794</v>
+        <v>433798</v>
       </c>
       <c r="R7" t="n">
-        <v>7068730</v>
+        <v>7068699</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126013</v>
+        <v>123126018</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433669</v>
+        <v>433754</v>
       </c>
       <c r="R8" t="n">
-        <v>7068887</v>
+        <v>7068779</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126032</v>
+        <v>123126021</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433626</v>
+        <v>433738</v>
       </c>
       <c r="R9" t="n">
-        <v>7068579</v>
+        <v>7068735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126023</v>
+        <v>123126010</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433765</v>
+        <v>433601</v>
       </c>
       <c r="R10" t="n">
-        <v>7068743</v>
+        <v>7068918</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126008</v>
+        <v>123126023</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433615</v>
+        <v>433765</v>
       </c>
       <c r="R11" t="n">
-        <v>7068906</v>
+        <v>7068743</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126020</v>
+        <v>123126009</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433773</v>
+        <v>433602</v>
       </c>
       <c r="R12" t="n">
-        <v>7068763</v>
+        <v>7068916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126009</v>
+        <v>123126040</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433602</v>
+        <v>433621</v>
       </c>
       <c r="R13" t="n">
-        <v>7068916</v>
+        <v>7068780</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126012</v>
+        <v>123126030</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433691</v>
+        <v>433770</v>
       </c>
       <c r="R14" t="n">
-        <v>7068902</v>
+        <v>7068647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126017</v>
+        <v>123126015</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433722</v>
+        <v>433714</v>
       </c>
       <c r="R15" t="n">
-        <v>7068798</v>
+        <v>7068855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126014</v>
+        <v>123126041</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>90981</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433715</v>
+        <v>433610</v>
       </c>
       <c r="R16" t="n">
-        <v>7068850</v>
+        <v>7068788</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,11 +2267,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126039</v>
+        <v>123126013</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433621</v>
+        <v>433669</v>
       </c>
       <c r="R17" t="n">
-        <v>7068773</v>
+        <v>7068887</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2373,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126031</v>
+        <v>123126038</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2445,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433679</v>
+        <v>433606</v>
       </c>
       <c r="R18" t="n">
-        <v>7068621</v>
+        <v>7068765</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126028</v>
+        <v>123126017</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2552,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433775</v>
+        <v>433722</v>
       </c>
       <c r="R19" t="n">
-        <v>7068594</v>
+        <v>7068798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2587,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2614,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126026</v>
+        <v>123126035</v>
       </c>
       <c r="B20" t="n">
         <v>57481</v>
@@ -2659,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433798</v>
+        <v>433677</v>
       </c>
       <c r="R20" t="n">
-        <v>7068699</v>
+        <v>7068737</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2694,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126029</v>
+        <v>123126014</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433762</v>
+        <v>433715</v>
       </c>
       <c r="R21" t="n">
-        <v>7068668</v>
+        <v>7068850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2806,7 +2801,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126030</v>
+        <v>123126024</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433770</v>
+        <v>433794</v>
       </c>
       <c r="R22" t="n">
-        <v>7068647</v>
+        <v>7068730</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126018</v>
+        <v>123126031</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433754</v>
+        <v>433679</v>
       </c>
       <c r="R23" t="n">
-        <v>7068779</v>
+        <v>7068621</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126040</v>
+        <v>123126020</v>
       </c>
       <c r="B25" t="n">
         <v>57481</v>
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433621</v>
+        <v>433773</v>
       </c>
       <c r="R25" t="n">
-        <v>7068780</v>
+        <v>7068763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3261,7 +3256,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126007</v>
+        <v>123126032</v>
       </c>
       <c r="B26" t="n">
         <v>57481</v>
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433613</v>
+        <v>433626</v>
       </c>
       <c r="R26" t="n">
-        <v>7068884</v>
+        <v>7068579</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,7 +3363,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126021</v>
+        <v>123126028</v>
       </c>
       <c r="B27" t="n">
         <v>57481</v>
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433738</v>
+        <v>433775</v>
       </c>
       <c r="R27" t="n">
-        <v>7068735</v>
+        <v>7068594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,7 +3470,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126035</v>
+        <v>123126034</v>
       </c>
       <c r="B28" t="n">
         <v>57481</v>
@@ -3515,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433677</v>
+        <v>433666</v>
       </c>
       <c r="R28" t="n">
-        <v>7068737</v>
+        <v>7068732</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3555,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3582,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126041</v>
+        <v>123126019</v>
       </c>
       <c r="B29" t="n">
-        <v>90975</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3598,21 +3593,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433610</v>
+        <v>433752</v>
       </c>
       <c r="R29" t="n">
-        <v>7068788</v>
+        <v>7068781</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,6 +3653,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126015</v>
+        <v>123126012</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433714</v>
+        <v>433691</v>
       </c>
       <c r="R30" t="n">
-        <v>7068855</v>
+        <v>7068902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126011</v>
+        <v>123126007</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433698</v>
+        <v>433613</v>
       </c>
       <c r="R31" t="n">
-        <v>7068902</v>
+        <v>7068884</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126038</v>
+        <v>123126008</v>
       </c>
       <c r="B32" t="n">
         <v>57481</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433606</v>
+        <v>433615</v>
       </c>
       <c r="R32" t="n">
-        <v>7068765</v>
+        <v>7068906</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126039</v>
+        <v>123126010</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433621</v>
+        <v>433601</v>
       </c>
       <c r="R4" t="n">
-        <v>7068773</v>
+        <v>7068918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126011</v>
+        <v>123126029</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433698</v>
+        <v>433762</v>
       </c>
       <c r="R5" t="n">
-        <v>7068902</v>
+        <v>7068668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126029</v>
+        <v>123126017</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433762</v>
+        <v>433722</v>
       </c>
       <c r="R6" t="n">
-        <v>7068668</v>
+        <v>7068798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1228,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126026</v>
+        <v>123126009</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433798</v>
+        <v>433602</v>
       </c>
       <c r="R7" t="n">
-        <v>7068699</v>
+        <v>7068916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126018</v>
+        <v>123126012</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433754</v>
+        <v>433691</v>
       </c>
       <c r="R8" t="n">
-        <v>7068779</v>
+        <v>7068902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126021</v>
+        <v>123126020</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433738</v>
+        <v>433773</v>
       </c>
       <c r="R9" t="n">
-        <v>7068735</v>
+        <v>7068763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126010</v>
+        <v>123126031</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433601</v>
+        <v>433679</v>
       </c>
       <c r="R10" t="n">
-        <v>7068918</v>
+        <v>7068621</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126023</v>
+        <v>123126019</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433765</v>
+        <v>433752</v>
       </c>
       <c r="R11" t="n">
-        <v>7068743</v>
+        <v>7068781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1763,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126009</v>
+        <v>123126023</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433602</v>
+        <v>433765</v>
       </c>
       <c r="R12" t="n">
-        <v>7068916</v>
+        <v>7068743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126040</v>
+        <v>123126013</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433621</v>
+        <v>433669</v>
       </c>
       <c r="R13" t="n">
-        <v>7068780</v>
+        <v>7068887</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126015</v>
+        <v>123126041</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>90984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433714</v>
+        <v>433610</v>
       </c>
       <c r="R15" t="n">
-        <v>7068855</v>
+        <v>7068788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,11 +2160,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126041</v>
+        <v>123126014</v>
       </c>
       <c r="B16" t="n">
-        <v>90981</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2207,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433610</v>
+        <v>433715</v>
       </c>
       <c r="R16" t="n">
-        <v>7068788</v>
+        <v>7068850</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,6 +2262,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126013</v>
+        <v>123126034</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433669</v>
+        <v>433666</v>
       </c>
       <c r="R17" t="n">
-        <v>7068887</v>
+        <v>7068732</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126038</v>
+        <v>123126039</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433606</v>
+        <v>433621</v>
       </c>
       <c r="R18" t="n">
-        <v>7068765</v>
+        <v>7068773</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126017</v>
+        <v>123126021</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433722</v>
+        <v>433738</v>
       </c>
       <c r="R19" t="n">
-        <v>7068798</v>
+        <v>7068735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2614,7 +2614,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126035</v>
+        <v>123126026</v>
       </c>
       <c r="B20" t="n">
         <v>57481</v>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433677</v>
+        <v>433798</v>
       </c>
       <c r="R20" t="n">
-        <v>7068737</v>
+        <v>7068699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126014</v>
+        <v>123126032</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433715</v>
+        <v>433626</v>
       </c>
       <c r="R21" t="n">
-        <v>7068850</v>
+        <v>7068579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2828,7 +2828,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126024</v>
+        <v>123126015</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433794</v>
+        <v>433714</v>
       </c>
       <c r="R22" t="n">
-        <v>7068730</v>
+        <v>7068855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2935,7 +2935,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126031</v>
+        <v>123126007</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433679</v>
+        <v>433613</v>
       </c>
       <c r="R23" t="n">
-        <v>7068621</v>
+        <v>7068884</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126036</v>
+        <v>123126018</v>
       </c>
       <c r="B24" t="n">
         <v>57481</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433681</v>
+        <v>433754</v>
       </c>
       <c r="R24" t="n">
-        <v>7068744</v>
+        <v>7068779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,7 +3149,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126020</v>
+        <v>123126011</v>
       </c>
       <c r="B25" t="n">
         <v>57481</v>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433773</v>
+        <v>433698</v>
       </c>
       <c r="R25" t="n">
-        <v>7068763</v>
+        <v>7068902</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,7 +3256,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126032</v>
+        <v>123126028</v>
       </c>
       <c r="B26" t="n">
         <v>57481</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433626</v>
+        <v>433775</v>
       </c>
       <c r="R26" t="n">
-        <v>7068579</v>
+        <v>7068594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126028</v>
+        <v>123126040</v>
       </c>
       <c r="B27" t="n">
         <v>57481</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433775</v>
+        <v>433621</v>
       </c>
       <c r="R27" t="n">
-        <v>7068594</v>
+        <v>7068780</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126034</v>
+        <v>123126038</v>
       </c>
       <c r="B28" t="n">
         <v>57481</v>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433666</v>
+        <v>433606</v>
       </c>
       <c r="R28" t="n">
-        <v>7068732</v>
+        <v>7068765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,7 +3577,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126019</v>
+        <v>123126008</v>
       </c>
       <c r="B29" t="n">
         <v>57481</v>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433752</v>
+        <v>433615</v>
       </c>
       <c r="R29" t="n">
-        <v>7068781</v>
+        <v>7068906</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,7 +3684,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126012</v>
+        <v>123126024</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433691</v>
+        <v>433794</v>
       </c>
       <c r="R30" t="n">
-        <v>7068902</v>
+        <v>7068730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126007</v>
+        <v>123126036</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433613</v>
+        <v>433681</v>
       </c>
       <c r="R31" t="n">
-        <v>7068884</v>
+        <v>7068744</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126008</v>
+        <v>123126035</v>
       </c>
       <c r="B32" t="n">
         <v>57481</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433615</v>
+        <v>433677</v>
       </c>
       <c r="R32" t="n">
-        <v>7068906</v>
+        <v>7068737</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126041</v>
+        <v>123126030</v>
       </c>
       <c r="B14" t="n">
-        <v>90984</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433610</v>
+        <v>433770</v>
       </c>
       <c r="R14" t="n">
-        <v>7068788</v>
+        <v>7068647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,6 +2053,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126030</v>
+        <v>123126041</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>90984</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2119,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433770</v>
+        <v>433610</v>
       </c>
       <c r="R15" t="n">
-        <v>7068647</v>
+        <v>7068788</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,11 +2160,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,7 +2186,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126034</v>
+        <v>123126014</v>
       </c>
       <c r="B16" t="n">
         <v>57481</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433666</v>
+        <v>433715</v>
       </c>
       <c r="R16" t="n">
-        <v>7068732</v>
+        <v>7068850</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,7 +2293,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126039</v>
+        <v>123126034</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433621</v>
+        <v>433666</v>
       </c>
       <c r="R17" t="n">
-        <v>7068773</v>
+        <v>7068732</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126021</v>
+        <v>123126039</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433738</v>
+        <v>433621</v>
       </c>
       <c r="R18" t="n">
-        <v>7068735</v>
+        <v>7068773</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2507,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126014</v>
+        <v>123126021</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433715</v>
+        <v>433738</v>
       </c>
       <c r="R19" t="n">
-        <v>7068850</v>
+        <v>7068735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126010</v>
+        <v>123126023</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433601</v>
+        <v>433765</v>
       </c>
       <c r="R4" t="n">
-        <v>7068918</v>
+        <v>7068743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126029</v>
+        <v>123126028</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433762</v>
+        <v>433775</v>
       </c>
       <c r="R5" t="n">
-        <v>7068668</v>
+        <v>7068594</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126017</v>
+        <v>123126007</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433722</v>
+        <v>433613</v>
       </c>
       <c r="R6" t="n">
-        <v>7068798</v>
+        <v>7068884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126009</v>
+        <v>123126008</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433602</v>
+        <v>433615</v>
       </c>
       <c r="R7" t="n">
-        <v>7068916</v>
+        <v>7068906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126012</v>
+        <v>123126010</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433691</v>
+        <v>433601</v>
       </c>
       <c r="R8" t="n">
-        <v>7068902</v>
+        <v>7068918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126020</v>
+        <v>123126036</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433773</v>
+        <v>433681</v>
       </c>
       <c r="R9" t="n">
-        <v>7068763</v>
+        <v>7068744</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126031</v>
+        <v>123126024</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433679</v>
+        <v>433794</v>
       </c>
       <c r="R10" t="n">
-        <v>7068621</v>
+        <v>7068730</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126019</v>
+        <v>123126031</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433752</v>
+        <v>433679</v>
       </c>
       <c r="R11" t="n">
-        <v>7068781</v>
+        <v>7068621</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126023</v>
+        <v>123126018</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433765</v>
+        <v>433754</v>
       </c>
       <c r="R12" t="n">
-        <v>7068743</v>
+        <v>7068779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1870,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126013</v>
+        <v>123126038</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433669</v>
+        <v>433606</v>
       </c>
       <c r="R13" t="n">
-        <v>7068887</v>
+        <v>7068765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126030</v>
+        <v>123126013</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433770</v>
+        <v>433669</v>
       </c>
       <c r="R14" t="n">
-        <v>7068647</v>
+        <v>7068887</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126041</v>
+        <v>123126029</v>
       </c>
       <c r="B15" t="n">
-        <v>90984</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433610</v>
+        <v>433762</v>
       </c>
       <c r="R15" t="n">
-        <v>7068788</v>
+        <v>7068668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,6 +2160,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126014</v>
+        <v>123126034</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433715</v>
+        <v>433666</v>
       </c>
       <c r="R16" t="n">
-        <v>7068850</v>
+        <v>7068732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2271,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2293,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126034</v>
+        <v>123126012</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433666</v>
+        <v>433691</v>
       </c>
       <c r="R17" t="n">
-        <v>7068732</v>
+        <v>7068902</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126039</v>
+        <v>123126026</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433621</v>
+        <v>433798</v>
       </c>
       <c r="R18" t="n">
-        <v>7068773</v>
+        <v>7068699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126021</v>
+        <v>123126032</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433738</v>
+        <v>433626</v>
       </c>
       <c r="R19" t="n">
-        <v>7068735</v>
+        <v>7068579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126026</v>
+        <v>123126020</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433798</v>
+        <v>433773</v>
       </c>
       <c r="R20" t="n">
-        <v>7068699</v>
+        <v>7068763</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,7 +2699,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,10 +2726,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126032</v>
+        <v>123126030</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433626</v>
+        <v>433770</v>
       </c>
       <c r="R21" t="n">
-        <v>7068579</v>
+        <v>7068647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126015</v>
+        <v>123126019</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433714</v>
+        <v>433752</v>
       </c>
       <c r="R22" t="n">
-        <v>7068855</v>
+        <v>7068781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2935,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126007</v>
+        <v>123126015</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433613</v>
+        <v>433714</v>
       </c>
       <c r="R23" t="n">
-        <v>7068884</v>
+        <v>7068855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126018</v>
+        <v>123126011</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433754</v>
+        <v>433698</v>
       </c>
       <c r="R24" t="n">
-        <v>7068779</v>
+        <v>7068902</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3127,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,10 +3154,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126011</v>
+        <v>123126017</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433698</v>
+        <v>433722</v>
       </c>
       <c r="R25" t="n">
-        <v>7068902</v>
+        <v>7068798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,10 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126028</v>
+        <v>123126035</v>
       </c>
       <c r="B26" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433775</v>
+        <v>433677</v>
       </c>
       <c r="R26" t="n">
-        <v>7068594</v>
+        <v>7068737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3363,10 +3368,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126040</v>
+        <v>123126041</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>91001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3379,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3403,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433621</v>
+        <v>433610</v>
       </c>
       <c r="R27" t="n">
-        <v>7068780</v>
+        <v>7068788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,11 +3444,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,10 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126038</v>
+        <v>123126040</v>
       </c>
       <c r="B28" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433606</v>
+        <v>433621</v>
       </c>
       <c r="R28" t="n">
-        <v>7068765</v>
+        <v>7068780</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126008</v>
+        <v>123126021</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433615</v>
+        <v>433738</v>
       </c>
       <c r="R29" t="n">
-        <v>7068906</v>
+        <v>7068735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3684,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126024</v>
+        <v>123126014</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433794</v>
+        <v>433715</v>
       </c>
       <c r="R30" t="n">
-        <v>7068730</v>
+        <v>7068850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126036</v>
+        <v>123126039</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433681</v>
+        <v>433621</v>
       </c>
       <c r="R31" t="n">
-        <v>7068744</v>
+        <v>7068773</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,10 +3898,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126035</v>
+        <v>123126009</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433677</v>
+        <v>433602</v>
       </c>
       <c r="R32" t="n">
-        <v>7068737</v>
+        <v>7068916</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126023</v>
+        <v>123126036</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433765</v>
+        <v>433681</v>
       </c>
       <c r="R4" t="n">
-        <v>7068743</v>
+        <v>7068744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126028</v>
+        <v>123126012</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433775</v>
+        <v>433691</v>
       </c>
       <c r="R5" t="n">
-        <v>7068594</v>
+        <v>7068902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126007</v>
+        <v>123126021</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433613</v>
+        <v>433738</v>
       </c>
       <c r="R6" t="n">
-        <v>7068884</v>
+        <v>7068735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126008</v>
+        <v>123126041</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433615</v>
+        <v>433610</v>
       </c>
       <c r="R7" t="n">
-        <v>7068906</v>
+        <v>7068788</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,11 +1304,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126010</v>
+        <v>123126032</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433601</v>
+        <v>433626</v>
       </c>
       <c r="R8" t="n">
-        <v>7068918</v>
+        <v>7068579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126036</v>
+        <v>123126013</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433681</v>
+        <v>433669</v>
       </c>
       <c r="R9" t="n">
-        <v>7068744</v>
+        <v>7068887</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1517,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126024</v>
+        <v>123126008</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433794</v>
+        <v>433615</v>
       </c>
       <c r="R10" t="n">
-        <v>7068730</v>
+        <v>7068906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1624,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126031</v>
+        <v>123126028</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433679</v>
+        <v>433775</v>
       </c>
       <c r="R11" t="n">
-        <v>7068621</v>
+        <v>7068594</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126018</v>
+        <v>123126020</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433754</v>
+        <v>433773</v>
       </c>
       <c r="R12" t="n">
-        <v>7068779</v>
+        <v>7068763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126038</v>
+        <v>123126010</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433606</v>
+        <v>433601</v>
       </c>
       <c r="R13" t="n">
-        <v>7068765</v>
+        <v>7068918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,7 +1945,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126013</v>
+        <v>123126019</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2017,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433669</v>
+        <v>433752</v>
       </c>
       <c r="R14" t="n">
-        <v>7068887</v>
+        <v>7068781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126029</v>
+        <v>123126024</v>
       </c>
       <c r="B15" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433762</v>
+        <v>433794</v>
       </c>
       <c r="R15" t="n">
-        <v>7068668</v>
+        <v>7068730</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2159,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126034</v>
+        <v>123126030</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433666</v>
+        <v>433770</v>
       </c>
       <c r="R16" t="n">
-        <v>7068732</v>
+        <v>7068647</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,7 +2266,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2298,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126012</v>
+        <v>123126009</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2338,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433691</v>
+        <v>433602</v>
       </c>
       <c r="R17" t="n">
-        <v>7068902</v>
+        <v>7068916</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2373,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126026</v>
+        <v>123126035</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2445,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433798</v>
+        <v>433677</v>
       </c>
       <c r="R18" t="n">
-        <v>7068699</v>
+        <v>7068737</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2480,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126032</v>
+        <v>123126007</v>
       </c>
       <c r="B19" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2552,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433626</v>
+        <v>433613</v>
       </c>
       <c r="R19" t="n">
-        <v>7068579</v>
+        <v>7068884</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2614,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126020</v>
+        <v>123126038</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2659,10 +2654,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433773</v>
+        <v>433606</v>
       </c>
       <c r="R20" t="n">
-        <v>7068763</v>
+        <v>7068765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2694,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,10 +2721,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126030</v>
+        <v>123126031</v>
       </c>
       <c r="B21" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433770</v>
+        <v>433679</v>
       </c>
       <c r="R21" t="n">
-        <v>7068647</v>
+        <v>7068621</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,10 +2828,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126019</v>
+        <v>123126014</v>
       </c>
       <c r="B22" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433752</v>
+        <v>433715</v>
       </c>
       <c r="R22" t="n">
-        <v>7068781</v>
+        <v>7068850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2908,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,10 +2935,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126015</v>
+        <v>123126017</v>
       </c>
       <c r="B23" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,10 +2975,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433714</v>
+        <v>433722</v>
       </c>
       <c r="R23" t="n">
-        <v>7068855</v>
+        <v>7068798</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3015,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3047,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126011</v>
+        <v>123126034</v>
       </c>
       <c r="B24" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3087,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433698</v>
+        <v>433666</v>
       </c>
       <c r="R24" t="n">
-        <v>7068902</v>
+        <v>7068732</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3127,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3154,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126017</v>
+        <v>123126011</v>
       </c>
       <c r="B25" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433722</v>
+        <v>433698</v>
       </c>
       <c r="R25" t="n">
-        <v>7068798</v>
+        <v>7068902</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,10 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126035</v>
+        <v>123126023</v>
       </c>
       <c r="B26" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433677</v>
+        <v>433765</v>
       </c>
       <c r="R26" t="n">
-        <v>7068737</v>
+        <v>7068743</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,10 +3363,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126041</v>
+        <v>123126040</v>
       </c>
       <c r="B27" t="n">
-        <v>91001</v>
+        <v>57490</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3384,21 +3379,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433610</v>
+        <v>433621</v>
       </c>
       <c r="R27" t="n">
-        <v>7068788</v>
+        <v>7068780</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,6 +3439,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,10 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126040</v>
+        <v>123126026</v>
       </c>
       <c r="B28" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433621</v>
+        <v>433798</v>
       </c>
       <c r="R28" t="n">
-        <v>7068780</v>
+        <v>7068699</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126021</v>
+        <v>123126018</v>
       </c>
       <c r="B29" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433738</v>
+        <v>433754</v>
       </c>
       <c r="R29" t="n">
-        <v>7068735</v>
+        <v>7068779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126014</v>
+        <v>123126029</v>
       </c>
       <c r="B30" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433715</v>
+        <v>433762</v>
       </c>
       <c r="R30" t="n">
-        <v>7068850</v>
+        <v>7068668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3794,7 +3794,7 @@
         <v>123126039</v>
       </c>
       <c r="B31" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3898,10 +3898,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126009</v>
+        <v>123126015</v>
       </c>
       <c r="B32" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433602</v>
+        <v>433714</v>
       </c>
       <c r="R32" t="n">
-        <v>7068916</v>
+        <v>7068855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126036</v>
+        <v>123126013</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433681</v>
+        <v>433669</v>
       </c>
       <c r="R4" t="n">
-        <v>7068744</v>
+        <v>7068887</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126012</v>
+        <v>123126031</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433691</v>
+        <v>433679</v>
       </c>
       <c r="R5" t="n">
-        <v>7068902</v>
+        <v>7068621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126021</v>
+        <v>123126030</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433738</v>
+        <v>433770</v>
       </c>
       <c r="R6" t="n">
-        <v>7068735</v>
+        <v>7068647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126041</v>
+        <v>123126034</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433610</v>
+        <v>433666</v>
       </c>
       <c r="R7" t="n">
-        <v>7068788</v>
+        <v>7068732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,6 +1304,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126032</v>
+        <v>123126029</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433626</v>
+        <v>433762</v>
       </c>
       <c r="R8" t="n">
-        <v>7068579</v>
+        <v>7068668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126013</v>
+        <v>123126028</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433669</v>
+        <v>433775</v>
       </c>
       <c r="R9" t="n">
-        <v>7068887</v>
+        <v>7068594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1522,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126008</v>
+        <v>123126009</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433615</v>
+        <v>433602</v>
       </c>
       <c r="R10" t="n">
-        <v>7068906</v>
+        <v>7068916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126028</v>
+        <v>123126038</v>
       </c>
       <c r="B11" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433775</v>
+        <v>433606</v>
       </c>
       <c r="R11" t="n">
-        <v>7068594</v>
+        <v>7068765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126020</v>
+        <v>123126010</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433773</v>
+        <v>433601</v>
       </c>
       <c r="R12" t="n">
-        <v>7068763</v>
+        <v>7068918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,7 +1843,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123126010</v>
+        <v>123126019</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433601</v>
+        <v>433752</v>
       </c>
       <c r="R13" t="n">
-        <v>7068918</v>
+        <v>7068781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126019</v>
+        <v>123126023</v>
       </c>
       <c r="B14" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2012,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433752</v>
+        <v>433765</v>
       </c>
       <c r="R14" t="n">
-        <v>7068781</v>
+        <v>7068743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2057,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126024</v>
+        <v>123126018</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2119,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433794</v>
+        <v>433754</v>
       </c>
       <c r="R15" t="n">
-        <v>7068730</v>
+        <v>7068779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126030</v>
+        <v>123126007</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433770</v>
+        <v>433613</v>
       </c>
       <c r="R16" t="n">
-        <v>7068647</v>
+        <v>7068884</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126009</v>
+        <v>123126021</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2333,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433602</v>
+        <v>433738</v>
       </c>
       <c r="R17" t="n">
-        <v>7068916</v>
+        <v>7068735</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2405,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126035</v>
+        <v>123126011</v>
       </c>
       <c r="B18" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433677</v>
+        <v>433698</v>
       </c>
       <c r="R18" t="n">
-        <v>7068737</v>
+        <v>7068902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126007</v>
+        <v>123126008</v>
       </c>
       <c r="B19" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2547,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433613</v>
+        <v>433615</v>
       </c>
       <c r="R19" t="n">
-        <v>7068884</v>
+        <v>7068906</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2614,10 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126038</v>
+        <v>123126024</v>
       </c>
       <c r="B20" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433606</v>
+        <v>433794</v>
       </c>
       <c r="R20" t="n">
-        <v>7068765</v>
+        <v>7068730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2721,10 +2726,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126031</v>
+        <v>123126040</v>
       </c>
       <c r="B21" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433679</v>
+        <v>433621</v>
       </c>
       <c r="R21" t="n">
-        <v>7068621</v>
+        <v>7068780</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2828,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126014</v>
+        <v>123126026</v>
       </c>
       <c r="B22" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2868,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433715</v>
+        <v>433798</v>
       </c>
       <c r="R22" t="n">
-        <v>7068850</v>
+        <v>7068699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2935,10 +2940,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126017</v>
+        <v>123126041</v>
       </c>
       <c r="B23" t="n">
-        <v>57490</v>
+        <v>91008</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2951,21 +2956,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2975,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433722</v>
+        <v>433610</v>
       </c>
       <c r="R23" t="n">
-        <v>7068798</v>
+        <v>7068788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3011,11 +3016,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126034</v>
+        <v>123126012</v>
       </c>
       <c r="B24" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433666</v>
+        <v>433691</v>
       </c>
       <c r="R24" t="n">
-        <v>7068732</v>
+        <v>7068902</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126011</v>
+        <v>123126020</v>
       </c>
       <c r="B25" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433698</v>
+        <v>433773</v>
       </c>
       <c r="R25" t="n">
-        <v>7068902</v>
+        <v>7068763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,10 +3256,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126023</v>
+        <v>123126014</v>
       </c>
       <c r="B26" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433765</v>
+        <v>433715</v>
       </c>
       <c r="R26" t="n">
-        <v>7068743</v>
+        <v>7068850</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126040</v>
+        <v>123126015</v>
       </c>
       <c r="B27" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433621</v>
+        <v>433714</v>
       </c>
       <c r="R27" t="n">
-        <v>7068780</v>
+        <v>7068855</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,10 +3470,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126026</v>
+        <v>123126036</v>
       </c>
       <c r="B28" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433798</v>
+        <v>433681</v>
       </c>
       <c r="R28" t="n">
-        <v>7068699</v>
+        <v>7068744</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123126018</v>
+        <v>123126039</v>
       </c>
       <c r="B29" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433754</v>
+        <v>433621</v>
       </c>
       <c r="R29" t="n">
-        <v>7068779</v>
+        <v>7068773</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3684,10 +3684,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126029</v>
+        <v>123126035</v>
       </c>
       <c r="B30" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433762</v>
+        <v>433677</v>
       </c>
       <c r="R30" t="n">
-        <v>7068668</v>
+        <v>7068737</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123126039</v>
+        <v>123126032</v>
       </c>
       <c r="B31" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433621</v>
+        <v>433626</v>
       </c>
       <c r="R31" t="n">
-        <v>7068773</v>
+        <v>7068579</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3898,10 +3898,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123126015</v>
+        <v>123126017</v>
       </c>
       <c r="B32" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433714</v>
+        <v>433722</v>
       </c>
       <c r="R32" t="n">
-        <v>7068855</v>
+        <v>7068798</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65011495</v>
+        <v>123126007</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V storflon, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433791.0851426424</v>
+        <v>433613</v>
       </c>
       <c r="R2" t="n">
-        <v>7068706.143605079</v>
+        <v>7068884</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65011496</v>
+        <v>123126008</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V storflon, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433652.2140794406</v>
+        <v>433615</v>
       </c>
       <c r="R3" t="n">
-        <v>7068831.329717648</v>
+        <v>7068906</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123126013</v>
+        <v>123126009</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433669</v>
+        <v>433602</v>
       </c>
       <c r="R4" t="n">
-        <v>7068887</v>
+        <v>7068916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123126031</v>
+        <v>123126010</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433679</v>
+        <v>433601</v>
       </c>
       <c r="R5" t="n">
-        <v>7068621</v>
+        <v>7068918</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123126030</v>
+        <v>123126011</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433770</v>
+        <v>433698</v>
       </c>
       <c r="R6" t="n">
-        <v>7068647</v>
+        <v>7068902</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123126034</v>
+        <v>123126012</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433666</v>
+        <v>433691</v>
       </c>
       <c r="R7" t="n">
-        <v>7068732</v>
+        <v>7068902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123126029</v>
+        <v>123126013</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433762</v>
+        <v>433669</v>
       </c>
       <c r="R8" t="n">
-        <v>7068668</v>
+        <v>7068887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123126028</v>
+        <v>123126014</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433775</v>
+        <v>433715</v>
       </c>
       <c r="R9" t="n">
-        <v>7068594</v>
+        <v>7068850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123126009</v>
+        <v>123126015</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433602</v>
+        <v>433714</v>
       </c>
       <c r="R10" t="n">
-        <v>7068916</v>
+        <v>7068855</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123126038</v>
+        <v>123126017</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433606</v>
+        <v>433722</v>
       </c>
       <c r="R11" t="n">
-        <v>7068765</v>
+        <v>7068798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123126010</v>
+        <v>123126018</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433601</v>
+        <v>433754</v>
       </c>
       <c r="R12" t="n">
-        <v>7068918</v>
+        <v>7068779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1843,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1873,12 +1800,7 @@
         <v>123126019</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123126023</v>
+        <v>123126020</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433765</v>
+        <v>433773</v>
       </c>
       <c r="R14" t="n">
-        <v>7068743</v>
+        <v>7068763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,7 +1974,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2084,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123126018</v>
+        <v>123126021</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>433754</v>
+        <v>433738</v>
       </c>
       <c r="R15" t="n">
-        <v>7068779</v>
+        <v>7068735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123126007</v>
+        <v>123126023</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2231,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433613</v>
+        <v>433765</v>
       </c>
       <c r="R16" t="n">
-        <v>7068884</v>
+        <v>7068743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123126021</v>
+        <v>123126024</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433738</v>
+        <v>433794</v>
       </c>
       <c r="R17" t="n">
-        <v>7068735</v>
+        <v>7068730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2378,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123126011</v>
+        <v>123126026</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433698</v>
+        <v>433798</v>
       </c>
       <c r="R18" t="n">
-        <v>7068902</v>
+        <v>7068699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123126008</v>
+        <v>123126027</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433615</v>
+        <v>433808</v>
       </c>
       <c r="R19" t="n">
-        <v>7068906</v>
+        <v>7068575</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,15 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123126024</v>
+        <v>123126028</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2659,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433794</v>
+        <v>433775</v>
       </c>
       <c r="R20" t="n">
-        <v>7068730</v>
+        <v>7068594</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2699,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123126040</v>
+        <v>123126029</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2766,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>433621</v>
+        <v>433762</v>
       </c>
       <c r="R21" t="n">
-        <v>7068780</v>
+        <v>7068668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2833,15 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123126026</v>
+        <v>123126030</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>433798</v>
+        <v>433770</v>
       </c>
       <c r="R22" t="n">
-        <v>7068699</v>
+        <v>7068647</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2913,7 +2790,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,15 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123126041</v>
+        <v>123126031</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>433610</v>
+        <v>433679</v>
       </c>
       <c r="R23" t="n">
-        <v>7068788</v>
+        <v>7068621</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,6 +2888,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,15 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123126012</v>
+        <v>123126032</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3082,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>433691</v>
+        <v>433626</v>
       </c>
       <c r="R24" t="n">
-        <v>7068902</v>
+        <v>7068579</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +2994,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,15 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123126020</v>
+        <v>123126034</v>
       </c>
       <c r="B25" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>433773</v>
+        <v>433666</v>
       </c>
       <c r="R25" t="n">
-        <v>7068763</v>
+        <v>7068732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,15 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123126014</v>
+        <v>123126035</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3296,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>433715</v>
+        <v>433677</v>
       </c>
       <c r="R26" t="n">
-        <v>7068850</v>
+        <v>7068737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,7 +3198,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,15 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123126015</v>
+        <v>123126036</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433714</v>
+        <v>433681</v>
       </c>
       <c r="R27" t="n">
-        <v>7068855</v>
+        <v>7068744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3443,7 +3300,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3470,15 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123126036</v>
+        <v>123126038</v>
       </c>
       <c r="B28" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433681</v>
+        <v>433606</v>
       </c>
       <c r="R28" t="n">
-        <v>7068744</v>
+        <v>7068765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3580,12 +3432,7 @@
         <v>123126039</v>
       </c>
       <c r="B29" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3684,15 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123126035</v>
+        <v>123126040</v>
       </c>
       <c r="B30" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,10 +3566,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433677</v>
+        <v>433621</v>
       </c>
       <c r="R30" t="n">
-        <v>7068737</v>
+        <v>7068780</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,220 +3630,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>123126032</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>433626</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7068579</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>123126017</v>
-      </c>
-      <c r="B32" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Storflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>433722</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7068798</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61692-2024 artfynd.xlsx
+++ b/artfynd/A 61692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126007</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126008</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126009</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126010</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126011</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126013</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126014</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126015</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126017</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126018</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126019</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126020</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126021</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126024</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126027</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126028</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126029</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126030</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126031</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126032</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126034</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126035</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126036</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126038</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,6 +3668,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126039</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,8 +3775,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123126040</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>